--- a/artfynd/A 64709-2020 artfynd.xlsx
+++ b/artfynd/A 64709-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64709-2020 artfynd.xlsx
+++ b/artfynd/A 64709-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96573237</v>
+        <v>114555474</v>
       </c>
       <c r="B2" t="n">
-        <v>90841</v>
+        <v>91795</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,23 +708,24 @@
           <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelängesträsket, Nb</t>
+          <t>Norrbotten, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>809370.9326771232</v>
+        <v>809371</v>
       </c>
       <c r="R2" t="n">
-        <v>7319071.456187801</v>
+        <v>7319071</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,44 +763,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Låga</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Låga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Väg och Miljö AB, Klas Andersson, Mikael Andersson, Ursula Zinko, Andrea Lindberg, Björn Almqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -2307,10 +2272,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114555474</v>
+        <v>114555517</v>
       </c>
       <c r="B15" t="n">
-        <v>91795</v>
+        <v>96610</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2319,25 +2284,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2351,10 +2316,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>809371</v>
+        <v>809298</v>
       </c>
       <c r="R15" t="n">
-        <v>7319071</v>
+        <v>7319107</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2413,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114555517</v>
+        <v>114553360</v>
       </c>
       <c r="B16" t="n">
-        <v>96610</v>
+        <v>90288</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2425,25 +2390,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>850</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sälgtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Deviodontia pilaecystidiata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Hjortstam &amp; Ryvarden</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2457,10 +2422,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>809298</v>
+        <v>809438</v>
       </c>
       <c r="R16" t="n">
-        <v>7319107</v>
+        <v>7319037</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2512,116 +2477,10 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Mikael Andersson, Ursula Zinko, Andrea Lindberg, Björn Almqvist</t>
+          <t>Mikael Andersson, Björn Almqvist, Andrea Lindberg, Ursula Zinko, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>114553360</v>
-      </c>
-      <c r="B17" t="n">
-        <v>90288</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>850</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Sälgtagging</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Deviodontia pilaecystidiata</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(S.Lundell) Hjortstam &amp; Ryvarden</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Norrbotten, Nb</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>809438</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7319037</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Överluleå</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Mikael Andersson, Björn Almqvist, Andrea Lindberg, Ursula Zinko, Klas Andersson, Väg och Miljö AB</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
